--- a/important_mails_2026-08-31.xlsx
+++ b/important_mails_2026-08-31.xlsx
@@ -2145,7 +2145,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2160,73 +2160,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 06:47:57 +0000</t>
+          <t>Sun, 30 Aug 2026 13:18:02 +0000</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
+          <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
- A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
+          <t>RE:[CASE 13223475262]  Removing ASIN:B0DYTQ745J from existing
+ variation with Parent ASIN:B0HG43RTJ1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>96
-SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
- Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-Your product is a kit/set/pack. A Safety Data Sheet is required for each possible hazardous product from the kit/set/pack, as indicated below:
-color acrylic paint
-Air dry clay
-We inform you that your documentation/ SDS( s ) for: "color acrylic paint" have been reviewed and approved in our systems.
-● There are missing document( s ). We are also awaiting valid documentation/ SDS/( s ) for "Air dry clay".
-Until we receive the entire valid documentation, for all the possible hazardous products from the kit/set/pack, the hazard warnings for your products may not appear on the ASIN's product detail page and your products may be rejected by some fulfillment centers.
-For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
-Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For an</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 30 Aug 2026 13:18:02 +0000</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 13223475262]  Removing ASIN:B0DYTQ745J from existing
- variation with Parent ASIN:B0HG43RTJ1</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13223475262] Removing ASIN:B0DYTQ745J from existing variation with Parent ASIN:B0HG43RTJ1
@@ -2259,39 +2208,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:43:19 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2306,39 +2255,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:15:03 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -2355,39 +2304,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:13:08 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -2405,40 +2354,40 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:10:41 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -2456,39 +2405,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:08:46 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -2506,39 +2455,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 07:12:52 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -2556,40 +2505,40 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 07:12:42 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -2607,39 +2556,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 10:00:43 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13214292782] 创建或更新 ASIN 变体</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13214292782] 创建或更新 ASIN 变体
@@ -2673,39 +2622,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 10:00:35 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13214194642] 创建或更新 ASIN 变体</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13214194642] 创建或更新 ASIN 变体
@@ -2738,39 +2687,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:59:03 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Asistencia al Vendedor de Amazon &lt;merch.service05@amazon.es&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Resolución del número de caso: 13214253602</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 Resolución del número de caso: 13214253602
@@ -2790,39 +2739,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:11:26 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -2839,39 +2788,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:10:20 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -2889,40 +2838,40 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:09:31 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -2940,39 +2889,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:07:50 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -2990,39 +2939,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 07:12:00 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -3065,40 +3014,40 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 07:10:48 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -3116,39 +3065,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 07:10:45 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -3166,39 +3115,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 13:09:12 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>New Selection Program benefits are now live</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>New Selection Program (2026) benefits are now live
  New Selection Program benefits are now live
@@ -3214,39 +3163,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 00:16:32 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA Grade and Resell is now available in Canada</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  A new way to recover value from your FBA returns
@@ -3267,83 +3216,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 24 Aug 2026 09:57:03 +0000</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Activeer je aanbod voor Nederland voor Pan-EU FBA op uiterlijk 3
- september</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Voor Pan-EU FBA zijn aanbiedingen in Nederland vereist
- 96
- Voor Pan-EU FBA zijn aanbiedingen in Nederland vereist
-                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
- Hallo,
- Vanaf 3 september 2026 moeten alle P</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 04:57:59 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-10</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -3366,39 +3271,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 03:20:04 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -3422,39 +3327,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 15:43:49 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026
  96
@@ -3464,40 +3369,40 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 14:03:19 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Early access: Bring the trust of Prime to your ecommerce site with
  MCF</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Early access: Bring the trust of Prime to your ecommerce site with MCF
 Hi there,
@@ -3511,39 +3416,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 14:55:04 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -3566,39 +3471,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 14:36:21 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Balance paid on your Amazon seller account
@@ -3616,39 +3521,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 04:55:13 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3664,39 +3569,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 03:28:54 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3712,39 +3617,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 16:10:20 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3765,39 +3670,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 15:24:40 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3818,39 +3723,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 04:58:18 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3866,39 +3771,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 19 Aug 2026 16:12:03 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3919,39 +3824,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 05:03:01 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3967,39 +3872,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 04:53:18 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4015,39 +3920,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sun, 16 Aug 2026 04:55:15 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4063,39 +3968,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sun, 16 Aug 2026 02:33:51 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TGTg3P+M9T)</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4120,39 +4025,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4168,39 +4073,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 04:42:49 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4216,39 +4121,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 01:29:59 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4269,39 +4174,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 04:59:33 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4317,39 +4222,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 12:15:45 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (tynmf1KRa8)</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4369,39 +4274,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 05:20:43 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4417,39 +4322,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 05:46:43 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (m4n18h8HiD)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4474,39 +4379,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 05:00:42 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4522,39 +4427,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 10 Aug 2026 09:16:35 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4570,39 +4475,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 14:33:13 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $126.79 in an attempt to settle your Amazon seller account balance.
@@ -4618,39 +4523,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 04:49:49 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4666,39 +4571,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sat, 8 Aug 2026 14:11:22 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4719,39 +4624,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sat, 8 Aug 2026 05:00:20 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4767,39 +4672,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 17:55:17 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4820,39 +4725,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 04:52:01 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4868,39 +4773,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 17:19:22 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (PLBovnqz6i)</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4920,39 +4825,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 05:43:06 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4968,39 +4873,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 04:57:39 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5016,39 +4921,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 16:27:49 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (3rwPw0NlBZ)</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5068,39 +4973,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 04:52:33 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5116,39 +5021,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 04:46:25 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5164,39 +5069,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 04:49:15 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5212,39 +5117,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 17:14:31 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5261,39 +5166,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 17:14:20 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5313,39 +5218,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends Saturday, Aug. 29—Save $100 before it's full price</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596mz/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596n3/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
@@ -5361,40 +5266,40 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 10:16:19 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>The fireside chat we teased is here. Early-bird pricing ends next
  week.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bwt/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58bwx/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
@@ -5410,39 +5315,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:05:40 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5462,39 +5367,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:47 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5511,39 +5416,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:34 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5563,39 +5468,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 12:23:03 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>You're exactly who Accelerate was designed for</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-18/7z58zcm/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
 [Your next level starts here](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58zcq/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
@@ -5610,40 +5515,40 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Live at Accelerate 2026: Mary Beth Westmoreland and Amit Agarwal
  fireside chat</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bxx/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58by1/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
@@ -5656,39 +5561,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:27:13 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5705,39 +5610,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:26:45 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5757,39 +5662,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:39:43 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5809,39 +5714,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:38:59 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5858,39 +5763,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:50 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5907,39 +5812,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:23 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5959,39 +5864,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 07:03:07 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>您的亚马逊卖家账户支付的余额</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 您的亚马逊卖家账户支付的余额
@@ -6020,40 +5925,40 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 13:25:55 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Did you catch Mary Beth's message? Early-bird extension ends August
  29</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-07/7z543yq/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z543yt/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
@@ -6067,39 +5972,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 15:01:57 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6116,39 +6021,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6168,39 +6073,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 13:10:07 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Hear from sellers who've been to Accelerate—92.9% of sellers said it was worth it</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-11/7z56gp4/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z56gp7/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
@@ -6215,39 +6120,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 12:45:09 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Mary Beth Westmoreland invites you to Amazon Accelerate 2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-07/7z543zx/6824284947/h/IMGEB96CBgyW2DY04pRCmrOMWOWCmWx4Su6ckkT2afE)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z54411/6824284947/h/IMGEB96CBgyW2DY04pRCmrOMWOWCmWx4Su6ckkT2afE)
@@ -6260,39 +6165,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 11:39:46 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6309,39 +6214,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 11:39:19 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6361,39 +6266,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 14:20:11 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6413,39 +6318,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 23:31:39 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6465,39 +6370,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 15:18:33 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6517,39 +6422,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 15:18:03 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6566,39 +6471,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 15:17:38 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6618,39 +6523,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 15:49:22 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.36. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -6664,39 +6569,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 15:22:13 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6720,39 +6625,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 12:59:47 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6769,39 +6674,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:39:35 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Final week of early-bird pricing for Amazon Accelerate 2026—ends August 8</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-29/7z4ytv7/6806510535/h/ebUC-rn_gdmnOZgc0Tgqz8DiEn0AwvkMsQeazFirtjo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4ytvb/6806510535/h/ebUC-rn_gdmnOZgc0Tgqz8DiEn0AwvkMsQeazFirtjo)
@@ -6820,39 +6725,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:14:10 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6872,39 +6777,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:13:54 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6921,39 +6826,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 09:02:05 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Managing compliance across Europe? There's a simpler way.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Managing compliance across Europe? There's a simpler way.
  96
@@ -6963,39 +6868,90 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 06:47:57 +0000</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
+ A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>96
+SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
+ Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+Your product is a kit/set/pack. A Safety Data Sheet is required for each possible hazardous product from the kit/set/pack, as indicated below:
+color acrylic paint
+Air dry clay
+We inform you that your documentation/ SDS( s ) for: "color acrylic paint" have been reviewed and approved in our systems.
+● There are missing document( s ). We are also awaiting valid documentation/ SDS/( s ) for "Air dry clay".
+Until we receive the entire valid documentation, for all the possible hazardous products from the kit/set/pack, the hazard warnings for your products may not appear on the ASIN's product detail page and your products may be rejected by some fulfillment centers.
+For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
+Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For an</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 16:08:02 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7013,39 +6969,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 23:14:29 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7063,39 +7019,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 12:34:53 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -7111,39 +7067,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 23:11:47 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7161,39 +7117,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 10:06:05 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -7220,39 +7176,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 16:08:49 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -7270,39 +7226,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 04:08:25 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7320,39 +7276,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 16:13:04 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Update tax information to prepare for UAE e-invoicing requirements</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Update tax information to prepare for UAE e-invoicing requirements
@@ -7367,39 +7323,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 17:07:34 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7417,39 +7373,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 16:07:16 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7468,39 +7424,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Mon, 10 Aug 2026 16:27:47 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Canada &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Your Tax Obligations on Amazon.ca</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
 Your Tax Obligations on Amazon.ca
@@ -7518,39 +7474,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Mon, 10 Aug 2026 11:54:13 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -7566,39 +7522,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 18:48:57 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7617,39 +7573,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 17:04:28 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour les ventes sur Amazon.fr |
 Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales
@@ -7662,39 +7618,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 13:27:26 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7713,39 +7669,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 19:14:34 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Zwrot kosztów zgodności z wymogami w zakresie opakowań w ramach ROP</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Rozpocznij rejestrację w ramach ROP przed 12 sierpnia, aby uzyskać częściowy zwrot kosztów w Szwecji i Polsce
@@ -7762,39 +7718,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 18:39:18 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7813,39 +7769,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 12:58:13 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2025 Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -7864,39 +7820,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 18:16:42 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7915,39 +7871,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 17:58:25 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7966,39 +7922,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:55:58 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8017,39 +7973,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:41:59 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8068,39 +8024,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 15:45:25 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -8127,39 +8083,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 09:15:08 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8177,39 +8133,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 03:48:43 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -8237,39 +8193,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 00:32:40 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8287,39 +8243,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 00:25:49 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8337,39 +8293,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 16:15:51 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -8387,39 +8343,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 15:08:44 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -8438,39 +8394,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 15:08:23 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello xiao jianming,
@@ -8486,39 +8442,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:23:21 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8536,39 +8492,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:17:26 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8586,39 +8542,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8634,39 +8590,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:10:39 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8679,6 +8635,50 @@
  To see the list of impacted ASINs in each store and reactivate your products, submit the required compliance documents by clicking ‘Add or appeal compliance’ next to the impacted ASIN on your ‘Manage your Compliance’ dashboard .
  We can only reinstate products that fulfil all relevant legal requirements for sale. Close, delete, or archive any non-compliant listings that you do not intend to sell or appeal in the future.
  What happens if I</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 09:57:03 +0000</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Activeer je aanbod voor Nederland voor Pan-EU FBA op uiterlijk 3
+ september</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Voor Pan-EU FBA zijn aanbiedingen in Nederland vereist
+ 96
+ Voor Pan-EU FBA zijn aanbiedingen in Nederland vereist
+                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
+ Hallo,
+ Vanaf 3 september 2026 moeten alle P</t>
         </is>
       </c>
     </row>
